--- a/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-pricing-calculator.xlsx
+++ b/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-pricing-calculator.xlsx
@@ -1050,10 +1050,10 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="32" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Rentals passed through (tables, linens, chafing dishes, tent)</t>
+          <t>Rentals for this event (your cost; they carry your margin)</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>What the rental company charges you for this event.</t>
+          <t>What the rental company charges you for tables, linens, chafing dishes or a tent. They sit in the direct cost, so the target margin applies to them too.</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
         <v>18.17536790415467</v>
       </c>
     </row>
-    <row r="92" ht="47" customHeight="1">
+    <row r="92" ht="62" customHeight="1">
       <c r="A92" s="15" t="inlineStr">
         <is>
           <t>PRICE PER GUEST before fees, service charge and tax</t>
@@ -1777,14 +1777,14 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Rounded up to the next 0.50. Market check: drop-off runs about $15-$30 per person and full-service up to $75 (q39kc.com); a Los Angeles operator charges $40-58 for parties and $65-85 for weddings (eventective.com).</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
+          <t>Rounded up to the next 0.50. While "Meat prices" says Missing, this price uses the package food cost estimate, not your meat prices. Market check: drop-off runs about $15-$30 per person and full-service up to $75 (q39kc.com); a Los Angeles operator charges $40-58 for parties and $65-85 for weddings (eventective.com).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="32" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Equivalent price per lb of cooked meat</t>
+          <t>All-in price per lb of cooked meat (sides, staff and margin included)</t>
         </is>
       </c>
       <c r="B93" s="17">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>The same price expressed per cooked pound, the way many drop-off menus quote.</t>
+          <t>The price per guest divided by the cooked meat per guest. It includes sides, staff, travel and margin, so do not compare it with by-the-pound menu prices for meat alone.</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>155 °F (68 °C) for 17 s (ground meat, sausage included)</t>
+          <t>155 °F (68 °C) for 17 s (ground meat, sausage included; 165 °F if it is chicken or turkey sausage)</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Keep the meat at 135 °F (57 °C) or above until you serve it.</t>
+          <t>Meat pans only: add carriers for hot sides such as mac and cheese and beans. Keep the food at 135 °F (57 °C) or above until you serve it.</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4139,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kit estimates for illustration. No meat price is typed here: until you type yours, the food cost uses the package estimate per guest, as in the "Pricing Calculator" tab. Each quote lands within 10% of the price of its line in the workbook's example mix ($22 drop-off, $35 party, $52 wedding). Change the inputs in "Pricing Calculator" to price your own events.</t>
+          <t>Kit estimates for illustration. No meat price is typed here: until you type yours, the food cost uses the package estimate per guest, as in the "Pricing Calculator" tab. Each quote lands within 10% of the price of its line in the example mix in the Word plan (section 3) ($22 drop-off, $35 party, $52 wedding). Change the inputs in "Pricing Calculator" to price your own events.</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Rentals passed through (tables, linens, chafing dishes, tent)</t>
+          <t>Rentals for this event (your cost; they carry your margin)</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
@@ -5695,7 +5695,7 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Equivalent price per lb of cooked meat</t>
+          <t>All-in price per lb of cooked meat (sides, staff and margin included)</t>
         </is>
       </c>
       <c r="B93" s="17">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Boxed BBQ lunch for an office, delivered and set (20-guest delivery minimum, as at hutchinsbbq.com). It lands within 10% of the $22 drop-off line in the workbook's example mix and inside the $15-$30 per person drop-off range (q39kc.com).</t>
+          <t>Boxed BBQ lunch for an office, delivered and set (20-guest delivery minimum, as at hutchinsbbq.com). It lands within 10% of the $22 drop-off line in the example mix of the Word plan (section 3) and inside the $15-$30 per person drop-off range (q39kc.com).</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Backyard graduation party with a staffed buffet and a carving station, 30-guest minimum. Within 10% of the $35 party line of the example mix, below the $40-58 that a Los Angeles operator charges for parties (eventective.com).</t>
+          <t>Backyard graduation party with a staffed buffet and a carving station, 30-guest minimum. Within 10% of the $35 party line of the example mix in the Word plan, below the $40-58 that a Los Angeles operator charges for parties (eventective.com).</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Full-service wedding with the smoker trailer on site for a $650 flat fee, rentals passed through and a 10% service charge; 75-guest minimum. The price per guest, with the live pit fee spread over the guests, lands within 10% of the $52 wedding line of the example mix, below the $65-85 of Los Angeles (eventective.com).</t>
+          <t>Full-service wedding with the smoker trailer on site for a $650 flat fee, rentals passed through and a 10% service charge; 75-guest minimum. The price per guest, with the live pit fee spread over the guests, lands within 10% of the $52 wedding line of the example mix in the Word plan, below the $65-85 of Los Angeles (eventective.com).</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
     <row r="5" ht="75" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>3. Enter sides, bread and sauces, disposables, wood, the live pit on site switch and its fee, your staff (event day and overnight cook hours), rentals and mileage. Then the marketplace fee, your target margin, the service charge, the sales tax rate and the switch "Does your state tax the service charge?". The price per guest is the direct cost divided by (1 - target margin - marketplace fee) and by the billable guests, rounded up to the next 0.50; the live pit fee and any event fee go on top. The tab also shows the same price per cooked lb.</t>
+          <t>3. Enter sides, bread and sauces, disposables, wood, the live pit on site switch and its fee, your staff (event day and overnight cook hours), rentals and mileage. Then the marketplace fee, your target margin, the service charge, the sales tax rate and the switch "Does your state tax the service charge?". The price per guest is the direct cost divided by (1 - target margin - marketplace fee) and by the billable guests, rounded up to the next 0.50; the live pit fee and any event fee go on top. The tab also shows that price per cooked lb, all-in: not comparable with by-the-pound menu prices.</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
     <row r="12" ht="75" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Cook to the minimum: 145 °F (63 °C) for 15 seconds for intact meat; 145 °F for 4 minutes for whole roasts; 155 °F (68 °C) for 17 seconds for injected, tenderized or ground meat, sausage included; 165 °F (74 °C) for poultry (3-401.11). Hold hot at 135 °F (57 °C) or above (3-501.16). Cool to 70 °F (21 °C) within 2 hours and to 41 °F (5 °C) within a total of 6 hours (3-501.14). Reheat for hot holding to 165 °F (3-403.11). The quality target of each cut is a different number: see the "Meat Yield &amp; Smoke Schedule" tab.</t>
+          <t>Cook to the minimum: 145 °F (63 °C) for 15 seconds for intact meat; 145 °F for 4 minutes for whole roasts; 155 °F (68 °C) for 17 seconds for injected, tenderized or ground meat, sausage included (165 °F for chicken or turkey sausage); 165 °F (74 °C) for poultry (3-401.11). Hold hot at 135 °F (57 °C) or above (3-501.16). Cool to 70 °F (21 °C) within 2 hours and to 41 °F (5 °C) within a total of 6 hours (3-501.14). Reheat for hot holding to 165 °F (3-403.11). The quality target of each cut is a different number: see the "Meat Yield &amp; Smoke Schedule" tab.</t>
         </is>
       </c>
     </row>
